--- a/ligacoes_ramal_1500.xlsx
+++ b/ligacoes_ramal_1500.xlsx
@@ -3403,7 +3403,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -38184,7 +38184,7 @@
         <v>15</v>
       </c>
       <c r="G1291" s="6" t="n">
-        <v>0.369270833333333</v>
+        <v>1.15740740740741E-005</v>
       </c>
       <c r="H1291" s="7" t="s">
         <v>1049</v>
